--- a/第十二道题/B/Q2_case3/output/case3/case3_summary.xlsx
+++ b/第十二道题/B/Q2_case3/output/case3/case3_summary.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="33" uniqueCount="11">
   <si>
     <t>CaseID</t>
   </si>
@@ -174,7 +174,7 @@
         <v>0</v>
       </c>
       <c r="K2" s="0">
-        <v>5.4946555999999998</v>
+        <v>5.1280823</v>
       </c>
     </row>
   </sheetData>
